--- a/Analysis/Prompt_Ablation/prompt_ablation_posthoc_tests.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_posthoc_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,31 +501,31 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7721.5</v>
+        <v>6323.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09531499286950784</v>
+        <v>6.27184108227982e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05351742274819198</v>
+        <v>-0.1653122945430638</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>195</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5718899572170471</v>
+        <v>0.0003763104649367892</v>
       </c>
       <c r="L2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7750</v>
+        <v>7206</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1030686898467172</v>
+        <v>0.005557448978869397</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05372781065088757</v>
+        <v>-0.09993425378040763</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         <v>195</v>
       </c>
       <c r="K3" t="n">
-        <v>0.515343449233586</v>
+        <v>0.02778724489434698</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +586,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>no_anchors</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8209.5</v>
+        <v>7676</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1714000665381105</v>
+        <v>0.06577301463894022</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04581196581196581</v>
+        <v>0.09556870479947403</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6856002661524419</v>
+        <v>0.2630920585557609</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8672</v>
+        <v>8075.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.375565758056344</v>
+        <v>0.09817429935809262</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03497698882314267</v>
+        <v>-0.1071137409598948</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         <v>195</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.2945228980742778</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -686,7 +686,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8909.5</v>
+        <v>8567</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5616222422686785</v>
+        <v>0.2105376083650431</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.009598948060486522</v>
+        <v>0.08499671268902038</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>195</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.4210752167300862</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7671</v>
+        <v>9352</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9655321439252218</v>
+        <v>0.7969783927609324</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009441157133464826</v>
+        <v>0.002998027613412229</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>195</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9655321439252218</v>
+        <v>0.7969783927609324</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -781,17 +781,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6323.5</v>
+        <v>3120</v>
       </c>
       <c r="G8" t="n">
-        <v>6.27184108227982e-05</v>
+        <v>9.808888937121852e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1653122945430638</v>
+        <v>0.2761078238001315</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>195</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0003763104649367892</v>
+        <v>2.942666681136556e-07</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -831,22 +831,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -855,24 +855,24 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7206</v>
+        <v>3238</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005557448978869397</v>
+        <v>0.0001119342467738097</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09993425378040763</v>
+        <v>-0.1902432610124918</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>195</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02778724489434698</v>
+        <v>0.0002238684935476195</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -881,22 +881,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7676</v>
+        <v>2887</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06577301463894022</v>
+        <v>0.003070951076930591</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09556870479947403</v>
+        <v>0.1164234056541749</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -922,309 +922,9 @@
         <v>195</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2630920585557609</v>
+        <v>0.003070951076930591</v>
       </c>
       <c r="L10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>8075.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.09817429935809262</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.1071137409598948</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>195</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2945228980742778</v>
-      </c>
-      <c r="L11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>8567</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.2105376083650431</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.08499671268902038</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>195</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.4210752167300862</v>
-      </c>
-      <c r="L12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>qwen</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>no_anchors</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>9352</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.7969783927609324</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.002998027613412229</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>195</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.7969783927609324</v>
-      </c>
-      <c r="L13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>3120</v>
-      </c>
-      <c r="G14" t="n">
-        <v>9.808888937121852e-08</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2761078238001315</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>195</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.942666681136556e-07</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>cot_scaffold</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>3238</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0001119342467738097</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.1902432610124918</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>small</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>195</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.0002238684935476195</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>deepseek</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>top1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>control</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>scale_0_10</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2887</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.003070951076930591</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1164234056541749</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>195</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.003070951076930591</v>
-      </c>
-      <c r="L16" t="b">
         <v>1</v>
       </c>
     </row>
